--- a/Files/testData.xlsx
+++ b/Files/testData.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,16 +77,13 @@
     <t>contactNo</t>
   </si>
   <si>
-    <t>resume</t>
-  </si>
-  <si>
     <t>notes</t>
   </si>
   <si>
     <t>vacancyName</t>
   </si>
   <si>
-    <t>ClickjobTitleOption</t>
+    <t>ClickJobTitleOption</t>
   </si>
   <si>
     <t>description</t>
@@ -113,25 +110,28 @@
     <t>admin123</t>
   </si>
   <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Kohli</t>
+  </si>
+  <si>
+    <t>EMP123</t>
+  </si>
+  <si>
+    <t>Rahul Kohli</t>
+  </si>
+  <si>
+    <t>Add Candidate</t>
+  </si>
+  <si>
     <t>Virat</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Kohli</t>
-  </si>
-  <si>
-    <t>EMP123</t>
-  </si>
-  <si>
-    <t>Virat Kohli</t>
-  </si>
-  <si>
-    <t>Add Candidate</t>
-  </si>
-  <si>
-    <t>Software Test Engineer</t>
+    <t>Test Automation Engineer IX</t>
   </si>
   <si>
     <t>abc@gmail.com</t>
@@ -146,16 +146,16 @@
     <t>Add Job Vacancy</t>
   </si>
   <si>
-    <t>Test Automation Engineer</t>
-  </si>
-  <si>
-    <t>Automaton Tester</t>
+    <t>QA Engineer</t>
   </si>
   <si>
     <t>Test Description</t>
   </si>
   <si>
-    <t>Ranga  Akunuri</t>
+    <t>a</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -1339,8 +1339,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W4"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <dimension ref="A1:V4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="12.1296296296296" customWidth="1"/>
@@ -1354,17 +1354,18 @@
     <col min="10" max="10" width="24.7777777777778" customWidth="1"/>
     <col min="11" max="11" width="9.75" customWidth="1"/>
     <col min="12" max="12" width="12.5" customWidth="1"/>
-    <col min="14" max="14" width="22.7777777777778" customWidth="1"/>
+    <col min="13" max="13" width="8.75"/>
+    <col min="14" max="14" width="27.8888888888889" customWidth="1"/>
     <col min="15" max="16" width="15.4444444444444" customWidth="1"/>
-    <col min="17" max="17" width="7.66666666666667" customWidth="1"/>
-    <col min="18" max="18" width="11.6666666666667" customWidth="1"/>
-    <col min="19" max="20" width="24.2222222222222" customWidth="1"/>
-    <col min="21" max="21" width="15.4444444444444" customWidth="1"/>
-    <col min="22" max="22" width="13.7777777777778" customWidth="1"/>
-    <col min="23" max="23" width="13.5555555555556" customWidth="1"/>
+    <col min="17" max="17" width="11.6666666666667" customWidth="1"/>
+    <col min="18" max="18" width="27.8888888888889" customWidth="1"/>
+    <col min="19" max="19" width="24.2222222222222" customWidth="1"/>
+    <col min="20" max="20" width="15.4444444444444" customWidth="1"/>
+    <col min="21" max="21" width="13.7777777777778" customWidth="1"/>
+    <col min="22" max="22" width="13.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1416,7 +1417,7 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="5" t="s">
@@ -1431,40 +1432,37 @@
       <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -1478,21 +1476,20 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:22">
       <c r="A3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -1500,11 +1497,11 @@
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N3" s="4" t="s">
         <v>34</v>
@@ -1515,29 +1512,28 @@
       <c r="P3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>37</v>
       </c>
+      <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
-      <c r="W3" s="4"/>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:22">
       <c r="A4" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -1551,7 +1547,9 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
+      <c r="R4" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="S4" s="4" t="s">
         <v>39</v>
       </c>
@@ -1561,11 +1559,8 @@
       <c r="U4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="V4" s="4" t="s">
+      <c r="V4" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="W4" s="4">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
